--- a/docs/Mapping_casi_uso/cittadinanza/Citt_049.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_049.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="168">
   <si>
     <t>Sezione</t>
   </si>
@@ -47,7 +47,7 @@
     <t/>
   </si>
   <si>
-    <t>Allegato aggiuntivo</t>
+    <t>Allegato generico</t>
   </si>
   <si>
     <t>NO</t>
@@ -327,6 +327,84 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>Id atto</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
+  </si>
+  <si>
+    <t>idAnsc</t>
+  </si>
+  <si>
+    <t>Provincia registrazione</t>
+  </si>
+  <si>
+    <t>idProvinciaRegistrazione</t>
+  </si>
+  <si>
+    <t>Provincia registrazione - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaRegistrazione</t>
+  </si>
+  <si>
+    <t>Comune registrazione</t>
+  </si>
+  <si>
+    <t>idComuneRegistrazione</t>
+  </si>
+  <si>
+    <t>Comune registrazione - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneRegistrazione</t>
+  </si>
+  <si>
+    <t>Tipo evento</t>
+  </si>
+  <si>
+    <t>idtipocontenuto</t>
+  </si>
+  <si>
+    <t>Numero Comunale</t>
+  </si>
+  <si>
+    <t>Anno atto</t>
+  </si>
+  <si>
+    <t>annoAtto</t>
+  </si>
+  <si>
+    <t>Data atto</t>
+  </si>
+  <si>
+    <t>Parte</t>
+  </si>
+  <si>
+    <t>parte</t>
+  </si>
+  <si>
+    <t>Serie</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>Tipo registro</t>
+  </si>
+  <si>
+    <t>tipologia</t>
   </si>
   <si>
     <t>Autorita mittente</t>
@@ -496,14 +574,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="55.49609375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="49.65234375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="24.66796875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="38.78125" customWidth="true" bestFit="true"/>
   </cols>
@@ -2149,7 +2227,7 @@
         <v>106</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>107</v>
@@ -2161,7 +2239,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
@@ -2172,7 +2250,7 @@
         <v>109</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>107</v>
@@ -2184,7 +2262,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74">
@@ -2195,7 +2273,7 @@
         <v>111</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>107</v>
@@ -2207,7 +2285,7 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75">
@@ -2218,7 +2296,7 @@
         <v>113</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>107</v>
@@ -2230,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76">
@@ -2241,7 +2319,7 @@
         <v>115</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>107</v>
@@ -2253,7 +2331,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77">
@@ -2276,7 +2354,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78">
@@ -2293,13 +2371,13 @@
         <v>107</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79">
@@ -2307,7 +2385,7 @@
         <v>105</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>12</v>
@@ -2316,13 +2394,13 @@
         <v>107</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80">
@@ -2330,7 +2408,7 @@
         <v>105</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>12</v>
@@ -2339,13 +2417,13 @@
         <v>107</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81">
@@ -2353,7 +2431,7 @@
         <v>105</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>12</v>
@@ -2362,1024 +2440,1323 @@
         <v>107</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>128</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>128</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>128</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>20</v>
+        <v>154</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="F127" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D128" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="F128" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F125" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G125" s="2" t="s">
+      <c r="C129" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="2" t="s">
         <v>20</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/cittadinanza/Citt_049.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_049.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="170">
   <si>
     <t>Sezione</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Data validità</t>
+  </si>
+  <si>
+    <t>dataValidita</t>
   </si>
   <si>
     <t>Atto collegato di Cittadinanza</t>
@@ -574,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
@@ -2221,39 +2227,39 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>110</v>
@@ -2267,7 +2273,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>111</v>
@@ -2276,7 +2282,7 @@
         <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>112</v>
@@ -2290,7 +2296,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>113</v>
@@ -2299,7 +2305,7 @@
         <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>114</v>
@@ -2313,7 +2319,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>115</v>
@@ -2322,7 +2328,7 @@
         <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>116</v>
@@ -2336,7 +2342,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>117</v>
@@ -2345,7 +2351,7 @@
         <v>12</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>118</v>
@@ -2359,7 +2365,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>119</v>
@@ -2368,10 +2374,10 @@
         <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2382,19 +2388,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2405,7 +2411,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>122</v>
@@ -2414,10 +2420,10 @@
         <v>12</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2428,19 +2434,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2451,7 +2457,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>125</v>
@@ -2460,7 +2466,7 @@
         <v>12</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>126</v>
@@ -2474,7 +2480,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>127</v>
@@ -2483,7 +2489,7 @@
         <v>12</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>128</v>
@@ -2497,7 +2503,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>129</v>
@@ -2506,7 +2512,7 @@
         <v>12</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>130</v>
@@ -2520,39 +2526,39 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>136</v>
@@ -2566,7 +2572,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>137</v>
@@ -2575,7 +2581,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>138</v>
@@ -2589,7 +2595,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>139</v>
@@ -2598,7 +2604,7 @@
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>140</v>
@@ -2612,7 +2618,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>141</v>
@@ -2621,7 +2627,7 @@
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>142</v>
@@ -2635,16 +2641,16 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>144</v>
@@ -2658,7 +2664,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>145</v>
@@ -2667,7 +2673,7 @@
         <v>12</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>146</v>
@@ -2681,7 +2687,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>147</v>
@@ -2690,7 +2696,7 @@
         <v>12</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>148</v>
@@ -2704,7 +2710,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>149</v>
@@ -2713,7 +2719,7 @@
         <v>12</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>150</v>
@@ -2727,19 +2733,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2750,755 +2756,755 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -3509,7 +3515,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>139</v>
@@ -3518,7 +3524,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>140</v>
@@ -3527,12 +3533,12 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>141</v>
@@ -3541,7 +3547,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>142</v>
@@ -3550,21 +3556,21 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>144</v>
@@ -3573,12 +3579,12 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>145</v>
@@ -3587,7 +3593,7 @@
         <v>12</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>146</v>
@@ -3596,12 +3602,12 @@
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>147</v>
@@ -3610,7 +3616,7 @@
         <v>12</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>148</v>
@@ -3619,12 +3625,12 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>149</v>
@@ -3633,7 +3639,7 @@
         <v>12</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>150</v>
@@ -3642,35 +3648,35 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E134" s="2" t="s">
+      <c r="F134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>159</v>
@@ -3679,7 +3685,7 @@
         <v>12</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>160</v>
@@ -3688,12 +3694,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>161</v>
@@ -3702,39 +3708,39 @@
         <v>12</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>20</v>
+        <v>158</v>
       </c>
     </row>
     <row r="138">
@@ -3742,21 +3748,44 @@
         <v>164</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="B139" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F138" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G138" s="2" t="s">
+      <c r="C139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>20</v>
       </c>
     </row>
